--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_la_araucania_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_la_araucania_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:21</t>
+    <t xml:space="preserve">2026-09-29 14:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_la_araucania_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_la_araucania_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:12</t>
+    <t xml:space="preserve">2026-09-29 18:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -487,7 +487,7 @@
         <v>7.58</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>39.75</v>
+        <v>39.74</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>32.16</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_la_araucania_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_la_araucania_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:47</t>
+    <t xml:space="preserve">2026-10-05 04:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -487,10 +487,10 @@
         <v>7.58</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>39.74</v>
+        <v>39.75</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>32.16</v>
+        <v>32.17</v>
       </c>
     </row>
     <row r="3">
